--- a/NECP Scenario/Results/Regional Results/THIRA_Capacity.xlsx
+++ b/NECP Scenario/Results/Regional Results/THIRA_Capacity.xlsx
@@ -533,25 +533,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3.304442308295706E-08</v>
+        <v>4.878631936723069E-08</v>
       </c>
       <c r="C3">
-        <v>3.322431649361883E-08</v>
+        <v>4.905084691190433E-08</v>
       </c>
       <c r="D3">
-        <v>1.827975636258853E-07</v>
+        <v>3.613475520737794E-07</v>
       </c>
       <c r="E3">
-        <v>5.074075635693452E-07</v>
+        <v>0.0102323350092463</v>
       </c>
       <c r="F3">
-        <v>0.0252799533764536</v>
+        <v>0.0628442324594997</v>
       </c>
       <c r="G3">
-        <v>0.0644932520689043</v>
+        <v>0.1128264968896918</v>
       </c>
       <c r="H3">
-        <v>0.1150111921016892</v>
+        <v>0.1646963524540606</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -793,25 +793,25 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.4000000000066074</v>
+        <v>0.4000000000071654</v>
       </c>
       <c r="C13">
-        <v>0.4000000000086521</v>
+        <v>0.4000000000101664</v>
       </c>
       <c r="D13">
-        <v>0.4000000000133036</v>
+        <v>0.4000000000161285</v>
       </c>
       <c r="E13">
-        <v>0.400000000024139</v>
+        <v>0.4000000000292054</v>
       </c>
       <c r="F13">
-        <v>0.4000000000410809</v>
+        <v>0.4000000000507783</v>
       </c>
       <c r="G13">
-        <v>0.4000000000759648</v>
+        <v>0.400000000094166</v>
       </c>
       <c r="H13">
-        <v>0.400000000423132</v>
+        <v>0.4000000005105067</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1163,19 +1163,19 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>0.0176212677327276</v>
+        <v>0.0131512949847639</v>
       </c>
       <c r="E27">
-        <v>0.0326144067506553</v>
+        <v>0.0374999066896532</v>
       </c>
       <c r="F27">
-        <v>0.0435733643149127</v>
+        <v>0.0435733640075223</v>
       </c>
       <c r="G27">
-        <v>0.0435733646921166</v>
+        <v>0.0435733645491178</v>
       </c>
       <c r="H27">
-        <v>0.0435733648674353</v>
+        <v>0.0435733648096347</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1215,19 +1215,19 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>5.50953469148505E-07</v>
+        <v>0.0261648627492277</v>
       </c>
       <c r="E29">
-        <v>0.0261648635235378</v>
+        <v>0.0261648637027625</v>
       </c>
       <c r="F29">
-        <v>0.0261648637834513</v>
+        <v>0.0261648638035307</v>
       </c>
       <c r="G29">
-        <v>0.0261648638693083</v>
+        <v>0.0261648638768253</v>
       </c>
       <c r="H29">
-        <v>0.0261648639402602</v>
+        <v>0.0261648639428002</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1319,19 +1319,19 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>0.2950045054137757</v>
+        <v>0.2792375243283402</v>
       </c>
       <c r="E33">
-        <v>0.334792387119079</v>
+        <v>0.3391122522310154</v>
       </c>
       <c r="F33">
-        <v>0.3827331041677649</v>
+        <v>0.375432853457418</v>
       </c>
       <c r="G33">
-        <v>0.3827331055803424</v>
+        <v>0.3815523309551836</v>
       </c>
       <c r="H33">
-        <v>0.4064160529034112</v>
+        <v>0.4067276664445908</v>
       </c>
     </row>
     <row r="34" spans="1:8">
